--- a/project-management/skills/pmo-pert-estimate/examples/scenario-3-mobile-app/pert-estimate.xlsx
+++ b/project-management/skills/pmo-pert-estimate/examples/scenario-3-mobile-app/pert-estimate.xlsx
@@ -8,10 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resources" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resource Plan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,9 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="8">
     <font>
       <name val="Calibri"/>
@@ -44,19 +41,18 @@
     </font>
     <font/>
     <font>
-      <b val="1"/>
-      <u val="single"/>
+      <i val="1"/>
     </font>
     <font>
-      <i val="1"/>
-      <sz val="9"/>
+      <b val="1"/>
+      <color rgb="FF9C0006"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="FFFF0000"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -85,17 +81,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFA500"/>
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -114,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -153,29 +144,18 @@
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3189,864 +3169,603 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Phase/WP/Activity</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>PERT Duration</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>σ</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>P6</t>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="I1" s="14" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="J1" s="14" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="K1" s="14" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="L1" s="14" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="M1" s="14" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="N1" s="14" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="O1" s="14" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="P1" s="14" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="Q1" s="14" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="R1" s="14" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="S1" s="14" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL (PD)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <f>WBS!A2</f>
-        <v/>
-      </c>
-      <c r="B2">
-        <f>WBS!B2&amp;IF(WBS!C2&lt;&gt;"", " "&amp;WBS!C2, "")&amp;IF(WBS!D2&lt;&gt;"", " "&amp;WBS!D2, "")</f>
-        <v/>
-      </c>
-      <c r="C2">
-        <f>WBS!L2</f>
-        <v/>
-      </c>
-      <c r="D2">
-        <f>WBS!M2</f>
-        <v/>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>Week of</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G2" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="H2" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="I2" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="J2" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="K2" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="L2" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="M2" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="N2" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="O2" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="P2" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Q2" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="R2" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="S2" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <f>WBS!A3</f>
-        <v/>
-      </c>
-      <c r="B3">
-        <f>WBS!B3&amp;IF(WBS!C3&lt;&gt;"", " "&amp;WBS!C3, "")&amp;IF(WBS!D3&lt;&gt;"", " "&amp;WBS!D3, "")</f>
-        <v/>
-      </c>
-      <c r="C3">
-        <f>WBS!L3</f>
-        <v/>
-      </c>
-      <c r="D3">
-        <f>WBS!M3</f>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Backend Dev</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BED</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>billable</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="E3" s="16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F3" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="17" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="J3" s="17" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="K3" s="17" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="L3" s="17" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="M3" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S3" s="16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="T3" s="18">
+        <f>SUM(D3:S3)</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <f>WBS!A4</f>
-        <v/>
-      </c>
-      <c r="B4">
-        <f>WBS!B4&amp;IF(WBS!C4&lt;&gt;"", " "&amp;WBS!C4, "")&amp;IF(WBS!D4&lt;&gt;"", " "&amp;WBS!D4, "")</f>
-        <v/>
-      </c>
-      <c r="C4">
-        <f>WBS!L4</f>
-        <v/>
-      </c>
-      <c r="D4">
-        <f>WBS!M4</f>
-        <v/>
-      </c>
-      <c r="E4" s="14" t="n"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mobile Dev</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MOB</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>billable</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="19" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="G4" s="19" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="H4" s="19" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="I4" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="19" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="N4" s="19" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="O4" s="19" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="P4" s="19" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="Q4" s="19" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="R4" s="16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S4" s="16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="T4" s="18">
+        <f>SUM(D4:S4)</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <f>WBS!A5</f>
-        <v/>
-      </c>
-      <c r="B5">
-        <f>WBS!B5&amp;IF(WBS!C5&lt;&gt;"", " "&amp;WBS!C5, "")&amp;IF(WBS!D5&lt;&gt;"", " "&amp;WBS!D5, "")</f>
-        <v/>
-      </c>
-      <c r="C5">
-        <f>WBS!L5</f>
-        <v/>
-      </c>
-      <c r="D5">
-        <f>WBS!M5</f>
-        <v/>
-      </c>
-      <c r="E5" s="14" t="n"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Product Owner</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>billable</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="I5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="18">
+        <f>SUM(D5:S5)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <f>WBS!A6</f>
-        <v/>
-      </c>
-      <c r="B6">
-        <f>WBS!B6&amp;IF(WBS!C6&lt;&gt;"", " "&amp;WBS!C6, "")&amp;IF(WBS!D6&lt;&gt;"", " "&amp;WBS!D6, "")</f>
-        <v/>
-      </c>
-      <c r="C6">
-        <f>WBS!L6</f>
-        <v/>
-      </c>
-      <c r="D6">
-        <f>WBS!M6</f>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>billable</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="J6" s="16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K6" s="16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L6" s="16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="M6" s="16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N6" s="16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="O6" s="16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P6" s="16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q6" s="16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="R6" s="16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S6" s="16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T6" s="18">
+        <f>SUM(D6:S6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <f>WBS!A7</f>
-        <v/>
-      </c>
-      <c r="B7">
-        <f>WBS!B7&amp;IF(WBS!C7&lt;&gt;"", " "&amp;WBS!C7, "")&amp;IF(WBS!D7&lt;&gt;"", " "&amp;WBS!D7, "")</f>
-        <v/>
-      </c>
-      <c r="C7">
-        <f>WBS!L7</f>
-        <v/>
-      </c>
-      <c r="D7">
-        <f>WBS!M7</f>
-        <v/>
-      </c>
-      <c r="E7" s="15" t="n"/>
-      <c r="F7" s="15" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <f>WBS!A8</f>
-        <v/>
-      </c>
-      <c r="B8">
-        <f>WBS!B8&amp;IF(WBS!C8&lt;&gt;"", " "&amp;WBS!C8, "")&amp;IF(WBS!D8&lt;&gt;"", " "&amp;WBS!D8, "")</f>
-        <v/>
-      </c>
-      <c r="C8">
-        <f>WBS!L8</f>
-        <v/>
-      </c>
-      <c r="D8">
-        <f>WBS!M8</f>
-        <v/>
-      </c>
-      <c r="F8" s="15" t="n"/>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Weekly TOTAL</t>
+        </is>
+      </c>
+      <c r="D7" s="12">
+        <f>SUM(D3:D6)</f>
+        <v/>
+      </c>
+      <c r="E7" s="12">
+        <f>SUM(E3:E6)</f>
+        <v/>
+      </c>
+      <c r="F7" s="12">
+        <f>SUM(F3:F6)</f>
+        <v/>
+      </c>
+      <c r="G7" s="12">
+        <f>SUM(G3:G6)</f>
+        <v/>
+      </c>
+      <c r="H7" s="12">
+        <f>SUM(H3:H6)</f>
+        <v/>
+      </c>
+      <c r="I7" s="12">
+        <f>SUM(I3:I6)</f>
+        <v/>
+      </c>
+      <c r="J7" s="12">
+        <f>SUM(J3:J6)</f>
+        <v/>
+      </c>
+      <c r="K7" s="12">
+        <f>SUM(K3:K6)</f>
+        <v/>
+      </c>
+      <c r="L7" s="12">
+        <f>SUM(L3:L6)</f>
+        <v/>
+      </c>
+      <c r="M7" s="12">
+        <f>SUM(M3:M6)</f>
+        <v/>
+      </c>
+      <c r="N7" s="12">
+        <f>SUM(N3:N6)</f>
+        <v/>
+      </c>
+      <c r="O7" s="12">
+        <f>SUM(O3:O6)</f>
+        <v/>
+      </c>
+      <c r="P7" s="12">
+        <f>SUM(P3:P6)</f>
+        <v/>
+      </c>
+      <c r="Q7" s="12">
+        <f>SUM(Q3:Q6)</f>
+        <v/>
+      </c>
+      <c r="R7" s="12">
+        <f>SUM(R3:R6)</f>
+        <v/>
+      </c>
+      <c r="S7" s="12">
+        <f>SUM(S3:S6)</f>
+        <v/>
+      </c>
+      <c r="T7" s="12">
+        <f>SUM(D7:S7)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <f>WBS!A9</f>
-        <v/>
-      </c>
-      <c r="B9">
-        <f>WBS!B9&amp;IF(WBS!C9&lt;&gt;"", " "&amp;WBS!C9, "")&amp;IF(WBS!D9&lt;&gt;"", " "&amp;WBS!D9, "")</f>
-        <v/>
-      </c>
-      <c r="C9">
-        <f>WBS!L9</f>
-        <v/>
-      </c>
-      <c r="D9">
-        <f>WBS!M9</f>
-        <v/>
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>Capacity Warnings</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <f>WBS!A10</f>
-        <v/>
-      </c>
-      <c r="B10">
-        <f>WBS!B10&amp;IF(WBS!C10&lt;&gt;"", " "&amp;WBS!C10, "")&amp;IF(WBS!D10&lt;&gt;"", " "&amp;WBS!D10, "")</f>
-        <v/>
-      </c>
-      <c r="C10">
-        <f>WBS!L10</f>
-        <v/>
-      </c>
-      <c r="D10">
-        <f>WBS!M10</f>
-        <v/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Overcommit: W6 (BED) (5.2 PD vs 5.0 PD capacity)</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <f>WBS!A11</f>
-        <v/>
-      </c>
-      <c r="B11">
-        <f>WBS!B11&amp;IF(WBS!C11&lt;&gt;"", " "&amp;WBS!C11, "")&amp;IF(WBS!D11&lt;&gt;"", " "&amp;WBS!D11, "")</f>
-        <v/>
-      </c>
-      <c r="C11">
-        <f>WBS!L11</f>
-        <v/>
-      </c>
-      <c r="D11">
-        <f>WBS!M11</f>
-        <v/>
-      </c>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="14" t="n"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Overcommit: W7 (BED) (5.2 PD vs 5.0 PD capacity)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <f>WBS!A12</f>
-        <v/>
-      </c>
-      <c r="B12">
-        <f>WBS!B12&amp;IF(WBS!C12&lt;&gt;"", " "&amp;WBS!C12, "")&amp;IF(WBS!D12&lt;&gt;"", " "&amp;WBS!D12, "")</f>
-        <v/>
-      </c>
-      <c r="C12">
-        <f>WBS!L12</f>
-        <v/>
-      </c>
-      <c r="D12">
-        <f>WBS!M12</f>
-        <v/>
-      </c>
-      <c r="F12" s="14" t="n"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Overcommit: W8 (BED) (5.2 PD vs 5.0 PD capacity)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <f>WBS!A13</f>
-        <v/>
-      </c>
-      <c r="B13">
-        <f>WBS!B13&amp;IF(WBS!C13&lt;&gt;"", " "&amp;WBS!C13, "")&amp;IF(WBS!D13&lt;&gt;"", " "&amp;WBS!D13, "")</f>
-        <v/>
-      </c>
-      <c r="C13">
-        <f>WBS!L13</f>
-        <v/>
-      </c>
-      <c r="D13">
-        <f>WBS!M13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14">
-        <f>WBS!A14</f>
-        <v/>
-      </c>
-      <c r="B14">
-        <f>WBS!B14&amp;IF(WBS!C14&lt;&gt;"", " "&amp;WBS!C14, "")&amp;IF(WBS!D14&lt;&gt;"", " "&amp;WBS!D14, "")</f>
-        <v/>
-      </c>
-      <c r="C14">
-        <f>WBS!L14</f>
-        <v/>
-      </c>
-      <c r="D14">
-        <f>WBS!M14</f>
-        <v/>
-      </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="14" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15">
-        <f>WBS!A15</f>
-        <v/>
-      </c>
-      <c r="B15">
-        <f>WBS!B15&amp;IF(WBS!C15&lt;&gt;"", " "&amp;WBS!C15, "")&amp;IF(WBS!D15&lt;&gt;"", " "&amp;WBS!D15, "")</f>
-        <v/>
-      </c>
-      <c r="C15">
-        <f>WBS!L15</f>
-        <v/>
-      </c>
-      <c r="D15">
-        <f>WBS!M15</f>
-        <v/>
-      </c>
-      <c r="G15" s="14" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <f>WBS!A16</f>
-        <v/>
-      </c>
-      <c r="B16">
-        <f>WBS!B16&amp;IF(WBS!C16&lt;&gt;"", " "&amp;WBS!C16, "")&amp;IF(WBS!D16&lt;&gt;"", " "&amp;WBS!D16, "")</f>
-        <v/>
-      </c>
-      <c r="C16">
-        <f>WBS!L16</f>
-        <v/>
-      </c>
-      <c r="D16">
-        <f>WBS!M16</f>
-        <v/>
-      </c>
-      <c r="G16" s="14" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <f>WBS!A17</f>
-        <v/>
-      </c>
-      <c r="B17">
-        <f>WBS!B17&amp;IF(WBS!C17&lt;&gt;"", " "&amp;WBS!C17, "")&amp;IF(WBS!D17&lt;&gt;"", " "&amp;WBS!D17, "")</f>
-        <v/>
-      </c>
-      <c r="C17">
-        <f>WBS!L17</f>
-        <v/>
-      </c>
-      <c r="D17">
-        <f>WBS!M17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18">
-        <f>WBS!A18</f>
-        <v/>
-      </c>
-      <c r="B18">
-        <f>WBS!B18&amp;IF(WBS!C18&lt;&gt;"", " "&amp;WBS!C18, "")&amp;IF(WBS!D18&lt;&gt;"", " "&amp;WBS!D18, "")</f>
-        <v/>
-      </c>
-      <c r="C18">
-        <f>WBS!L18</f>
-        <v/>
-      </c>
-      <c r="D18">
-        <f>WBS!M18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19">
-        <f>WBS!A19</f>
-        <v/>
-      </c>
-      <c r="B19">
-        <f>WBS!B19&amp;IF(WBS!C19&lt;&gt;"", " "&amp;WBS!C19, "")&amp;IF(WBS!D19&lt;&gt;"", " "&amp;WBS!D19, "")</f>
-        <v/>
-      </c>
-      <c r="C19">
-        <f>WBS!L19</f>
-        <v/>
-      </c>
-      <c r="D19">
-        <f>WBS!M19</f>
-        <v/>
-      </c>
-      <c r="F19" s="15" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20">
-        <f>WBS!A20</f>
-        <v/>
-      </c>
-      <c r="B20">
-        <f>WBS!B20&amp;IF(WBS!C20&lt;&gt;"", " "&amp;WBS!C20, "")&amp;IF(WBS!D20&lt;&gt;"", " "&amp;WBS!D20, "")</f>
-        <v/>
-      </c>
-      <c r="C20">
-        <f>WBS!L20</f>
-        <v/>
-      </c>
-      <c r="D20">
-        <f>WBS!M20</f>
-        <v/>
-      </c>
-      <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21">
-        <f>WBS!A21</f>
-        <v/>
-      </c>
-      <c r="B21">
-        <f>WBS!B21&amp;IF(WBS!C21&lt;&gt;"", " "&amp;WBS!C21, "")&amp;IF(WBS!D21&lt;&gt;"", " "&amp;WBS!D21, "")</f>
-        <v/>
-      </c>
-      <c r="C21">
-        <f>WBS!L21</f>
-        <v/>
-      </c>
-      <c r="D21">
-        <f>WBS!M21</f>
-        <v/>
-      </c>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22">
-        <f>WBS!A22</f>
-        <v/>
-      </c>
-      <c r="B22">
-        <f>WBS!B22&amp;IF(WBS!C22&lt;&gt;"", " "&amp;WBS!C22, "")&amp;IF(WBS!D22&lt;&gt;"", " "&amp;WBS!D22, "")</f>
-        <v/>
-      </c>
-      <c r="C22">
-        <f>WBS!L22</f>
-        <v/>
-      </c>
-      <c r="D22">
-        <f>WBS!M22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23">
-        <f>WBS!A23</f>
-        <v/>
-      </c>
-      <c r="B23">
-        <f>WBS!B23&amp;IF(WBS!C23&lt;&gt;"", " "&amp;WBS!C23, "")&amp;IF(WBS!D23&lt;&gt;"", " "&amp;WBS!D23, "")</f>
-        <v/>
-      </c>
-      <c r="C23">
-        <f>WBS!L23</f>
-        <v/>
-      </c>
-      <c r="D23">
-        <f>WBS!M23</f>
-        <v/>
-      </c>
-      <c r="F23" s="15" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24">
-        <f>WBS!A24</f>
-        <v/>
-      </c>
-      <c r="B24">
-        <f>WBS!B24&amp;IF(WBS!C24&lt;&gt;"", " "&amp;WBS!C24, "")&amp;IF(WBS!D24&lt;&gt;"", " "&amp;WBS!D24, "")</f>
-        <v/>
-      </c>
-      <c r="C24">
-        <f>WBS!L24</f>
-        <v/>
-      </c>
-      <c r="D24">
-        <f>WBS!M24</f>
-        <v/>
-      </c>
-      <c r="F24" s="15" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <f>WBS!A25</f>
-        <v/>
-      </c>
-      <c r="B25">
-        <f>WBS!B25&amp;IF(WBS!C25&lt;&gt;"", " "&amp;WBS!C25, "")&amp;IF(WBS!D25&lt;&gt;"", " "&amp;WBS!D25, "")</f>
-        <v/>
-      </c>
-      <c r="C25">
-        <f>WBS!L25</f>
-        <v/>
-      </c>
-      <c r="D25">
-        <f>WBS!M25</f>
-        <v/>
-      </c>
-      <c r="G25" s="15" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <f>WBS!A26</f>
-        <v/>
-      </c>
-      <c r="B26">
-        <f>WBS!B26&amp;IF(WBS!C26&lt;&gt;"", " "&amp;WBS!C26, "")&amp;IF(WBS!D26&lt;&gt;"", " "&amp;WBS!D26, "")</f>
-        <v/>
-      </c>
-      <c r="C26">
-        <f>WBS!L26</f>
-        <v/>
-      </c>
-      <c r="D26">
-        <f>WBS!M26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <f>WBS!A27</f>
-        <v/>
-      </c>
-      <c r="B27">
-        <f>WBS!B27&amp;IF(WBS!C27&lt;&gt;"", " "&amp;WBS!C27, "")&amp;IF(WBS!D27&lt;&gt;"", " "&amp;WBS!D27, "")</f>
-        <v/>
-      </c>
-      <c r="C27">
-        <f>WBS!L27</f>
-        <v/>
-      </c>
-      <c r="D27">
-        <f>WBS!M27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28">
-        <f>WBS!A28</f>
-        <v/>
-      </c>
-      <c r="B28">
-        <f>WBS!B28&amp;IF(WBS!C28&lt;&gt;"", " "&amp;WBS!C28, "")&amp;IF(WBS!D28&lt;&gt;"", " "&amp;WBS!D28, "")</f>
-        <v/>
-      </c>
-      <c r="C28">
-        <f>WBS!L28</f>
-        <v/>
-      </c>
-      <c r="D28">
-        <f>WBS!M28</f>
-        <v/>
-      </c>
-      <c r="G28" s="15" t="n"/>
-      <c r="H28" s="15" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29">
-        <f>WBS!A29</f>
-        <v/>
-      </c>
-      <c r="B29">
-        <f>WBS!B29&amp;IF(WBS!C29&lt;&gt;"", " "&amp;WBS!C29, "")&amp;IF(WBS!D29&lt;&gt;"", " "&amp;WBS!D29, "")</f>
-        <v/>
-      </c>
-      <c r="C29">
-        <f>WBS!L29</f>
-        <v/>
-      </c>
-      <c r="D29">
-        <f>WBS!M29</f>
-        <v/>
-      </c>
-      <c r="G29" s="14" t="n"/>
-      <c r="H29" s="14" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <f>WBS!A30</f>
-        <v/>
-      </c>
-      <c r="B30">
-        <f>WBS!B30&amp;IF(WBS!C30&lt;&gt;"", " "&amp;WBS!C30, "")&amp;IF(WBS!D30&lt;&gt;"", " "&amp;WBS!D30, "")</f>
-        <v/>
-      </c>
-      <c r="C30">
-        <f>WBS!L30</f>
-        <v/>
-      </c>
-      <c r="D30">
-        <f>WBS!M30</f>
-        <v/>
-      </c>
-      <c r="H30" s="14" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31">
-        <f>WBS!A31</f>
-        <v/>
-      </c>
-      <c r="B31">
-        <f>WBS!B31&amp;IF(WBS!C31&lt;&gt;"", " "&amp;WBS!C31, "")&amp;IF(WBS!D31&lt;&gt;"", " "&amp;WBS!D31, "")</f>
-        <v/>
-      </c>
-      <c r="C31">
-        <f>WBS!L31</f>
-        <v/>
-      </c>
-      <c r="D31">
-        <f>WBS!M31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32">
-        <f>WBS!A32</f>
-        <v/>
-      </c>
-      <c r="B32">
-        <f>WBS!B32&amp;IF(WBS!C32&lt;&gt;"", " "&amp;WBS!C32, "")&amp;IF(WBS!D32&lt;&gt;"", " "&amp;WBS!D32, "")</f>
-        <v/>
-      </c>
-      <c r="C32">
-        <f>WBS!L32</f>
-        <v/>
-      </c>
-      <c r="D32">
-        <f>WBS!M32</f>
-        <v/>
-      </c>
-      <c r="H32" s="15" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33">
-        <f>WBS!A33</f>
-        <v/>
-      </c>
-      <c r="B33">
-        <f>WBS!B33&amp;IF(WBS!C33&lt;&gt;"", " "&amp;WBS!C33, "")&amp;IF(WBS!D33&lt;&gt;"", " "&amp;WBS!D33, "")</f>
-        <v/>
-      </c>
-      <c r="C33">
-        <f>WBS!L33</f>
-        <v/>
-      </c>
-      <c r="D33">
-        <f>WBS!M33</f>
-        <v/>
-      </c>
-      <c r="H33" s="14" t="n"/>
-      <c r="I33" s="14" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34">
-        <f>WBS!A34</f>
-        <v/>
-      </c>
-      <c r="B34">
-        <f>WBS!B34&amp;IF(WBS!C34&lt;&gt;"", " "&amp;WBS!C34, "")&amp;IF(WBS!D34&lt;&gt;"", " "&amp;WBS!D34, "")</f>
-        <v/>
-      </c>
-      <c r="C34">
-        <f>WBS!L34</f>
-        <v/>
-      </c>
-      <c r="D34">
-        <f>WBS!M34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35">
-        <f>WBS!A35</f>
-        <v/>
-      </c>
-      <c r="B35">
-        <f>WBS!B35&amp;IF(WBS!C35&lt;&gt;"", " "&amp;WBS!C35, "")&amp;IF(WBS!D35&lt;&gt;"", " "&amp;WBS!D35, "")</f>
-        <v/>
-      </c>
-      <c r="C35">
-        <f>WBS!L35</f>
-        <v/>
-      </c>
-      <c r="D35">
-        <f>WBS!M35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36">
-        <f>WBS!A36</f>
-        <v/>
-      </c>
-      <c r="B36">
-        <f>WBS!B36&amp;IF(WBS!C36&lt;&gt;"", " "&amp;WBS!C36, "")&amp;IF(WBS!D36&lt;&gt;"", " "&amp;WBS!D36, "")</f>
-        <v/>
-      </c>
-      <c r="C36">
-        <f>WBS!L36</f>
-        <v/>
-      </c>
-      <c r="D36">
-        <f>WBS!M36</f>
-        <v/>
-      </c>
-      <c r="I36" s="14" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37">
-        <f>WBS!A37</f>
-        <v/>
-      </c>
-      <c r="B37">
-        <f>WBS!B37&amp;IF(WBS!C37&lt;&gt;"", " "&amp;WBS!C37, "")&amp;IF(WBS!D37&lt;&gt;"", " "&amp;WBS!D37, "")</f>
-        <v/>
-      </c>
-      <c r="C37">
-        <f>WBS!L37</f>
-        <v/>
-      </c>
-      <c r="D37">
-        <f>WBS!M37</f>
-        <v/>
-      </c>
-      <c r="I37" s="14" t="n"/>
-      <c r="J37" s="14" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38">
-        <f>WBS!A38</f>
-        <v/>
-      </c>
-      <c r="B38">
-        <f>WBS!B38&amp;IF(WBS!C38&lt;&gt;"", " "&amp;WBS!C38, "")&amp;IF(WBS!D38&lt;&gt;"", " "&amp;WBS!D38, "")</f>
-        <v/>
-      </c>
-      <c r="C38">
-        <f>WBS!L38</f>
-        <v/>
-      </c>
-      <c r="D38">
-        <f>WBS!M38</f>
-        <v/>
-      </c>
-      <c r="J38" s="14" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="16" t="inlineStr">
-        <is>
-          <t>Critical Path</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>1.1.1 → 1.1.2 → 2.1.1 → 2.1.2 → 2.2.1 → 2.2.2 → 2.2.3 → 4.1.2 → 4.1.3 → 4.2.2 → 5.1.1 → 5.1.2 → 5.1.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="16" t="inlineStr">
-        <is>
-          <t>Total PERT Duration</t>
-        </is>
-      </c>
-      <c r="B41">
-        <f>WBS!L39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="16" t="inlineStr">
-        <is>
-          <t>CI 68%</t>
-        </is>
-      </c>
-      <c r="B42">
-        <f>WBS!L39&amp;" ± "&amp;WBS!M39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="16" t="inlineStr">
-        <is>
-          <t>CI 95%</t>
-        </is>
-      </c>
-      <c r="B43">
-        <f>WBS!L39&amp;" ± 2×"&amp;WBS!M39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="16" t="inlineStr">
-        <is>
-          <t>Start Date</t>
-        </is>
-      </c>
-      <c r="B44" s="17" t="n">
-        <v>46204</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="16" t="inlineStr">
-        <is>
-          <t>End Date</t>
-        </is>
-      </c>
-      <c r="B45" s="17" t="n">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="18" t="inlineStr">
-        <is>
-          <t>Legend</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="14" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Critical Path</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="15" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Parallel Activity</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="19" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Continuous Activity</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Overcommit: W9 (BED) (5.2 PD vs 5.0 PD capacity)</t>
         </is>
       </c>
     </row>
@@ -4056,628 +3775,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="D1" s="20" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E1" s="20" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F1" s="20" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G1" s="20" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="21" t="inlineStr">
-        <is>
-          <t>Phase</t>
-        </is>
-      </c>
-      <c r="B2" s="21" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C2" s="21" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-      <c r="D2" s="22" t="inlineStr">
-        <is>
-          <t>Product Owner</t>
-        </is>
-      </c>
-      <c r="E2" s="22" t="inlineStr">
-        <is>
-          <t>Mobile Dev</t>
-        </is>
-      </c>
-      <c r="F2" s="22" t="inlineStr">
-        <is>
-          <t>Backend Dev</t>
-        </is>
-      </c>
-      <c r="G2" s="22" t="inlineStr">
-        <is>
-          <t>QA Engineer</t>
-        </is>
-      </c>
-      <c r="H2" s="22" t="inlineStr">
-        <is>
-          <t>TOTAL EFFORT</t>
-        </is>
-      </c>
-      <c r="I2" s="22" t="inlineStr">
-        <is>
-          <t>BILLABLE EFFORT</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Stakeholder alignment and technical feasibility</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D3" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="H3" s="24">
-        <f>SUM(D3:G3)</f>
-        <v/>
-      </c>
-      <c r="I3" s="24">
-        <f>SUMPRODUCT(D3:G3,(D$1:G$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>UX Design</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Wireframing and interactive prototype</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D4" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="H4" s="24">
-        <f>SUM(D4:G4)</f>
-        <v/>
-      </c>
-      <c r="I4" s="24">
-        <f>SUMPRODUCT(D4:G4,(D$1:G$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Launch</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>App store submission, UAT and go-live</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D5" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="H5" s="24">
-        <f>SUM(D5:G5)</f>
-        <v/>
-      </c>
-      <c r="I5" s="24">
-        <f>SUMPRODUCT(D5:G5,(D$1:G$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Subtotal — Product</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D6" s="25">
-        <f>SUM(D3,D4,D5)</f>
-        <v/>
-      </c>
-      <c r="E6" s="25">
-        <f>SUM(E3,E4,E5)</f>
-        <v/>
-      </c>
-      <c r="F6" s="25">
-        <f>SUM(F3,F4,F5)</f>
-        <v/>
-      </c>
-      <c r="G6" s="25">
-        <f>SUM(G3,G4,G5)</f>
-        <v/>
-      </c>
-      <c r="H6" s="26">
-        <f>SUM(D6:G6)</f>
-        <v/>
-      </c>
-      <c r="I6" s="26">
-        <f>SUMPRODUCT(D6:G6,(D$1:G$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Stakeholder alignment and technical feasibility</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" s="24">
-        <f>SUM(D7:G7)</f>
-        <v/>
-      </c>
-      <c r="I7" s="24">
-        <f>SUMPRODUCT(D7:G7,(D$1:G$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Stakeholder alignment and technical feasibility</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="H8" s="24">
-        <f>SUM(D8:G8)</f>
-        <v/>
-      </c>
-      <c r="I8" s="24">
-        <f>SUMPRODUCT(D8:G8,(D$1:G$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>UX Design</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Wireframing and interactive prototype</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E9" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="H9" s="24">
-        <f>SUM(D9:G9)</f>
-        <v/>
-      </c>
-      <c r="I9" s="24">
-        <f>SUMPRODUCT(D9:G9,(D$1:G$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>UX Design</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Wireframing and interactive prototype</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="G10" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="H10" s="24">
-        <f>SUM(D10:G10)</f>
-        <v/>
-      </c>
-      <c r="I10" s="24">
-        <f>SUMPRODUCT(D10:G10,(D$1:G$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Backend Development</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>REST API implementation and infrastructure</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="n">
-        <v>24</v>
-      </c>
-      <c r="H11" s="24">
-        <f>SUM(D11:G11)</f>
-        <v/>
-      </c>
-      <c r="I11" s="24">
-        <f>SUMPRODUCT(D11:G11,(D$1:G$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Backend Development</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>REST API implementation and infrastructure</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E12" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="H12" s="24">
-        <f>SUM(D12:G12)</f>
-        <v/>
-      </c>
-      <c r="I12" s="24">
-        <f>SUMPRODUCT(D12:G12,(D$1:G$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Backend Development</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>REST API implementation and infrastructure</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="G13" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" s="24">
-        <f>SUM(D13:G13)</f>
-        <v/>
-      </c>
-      <c r="I13" s="24">
-        <f>SUMPRODUCT(D13:G13,(D$1:G$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Mobile Development</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Cross-platform app implementation and testing</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="n">
-        <v>23</v>
-      </c>
-      <c r="H14" s="24">
-        <f>SUM(D14:G14)</f>
-        <v/>
-      </c>
-      <c r="I14" s="24">
-        <f>SUMPRODUCT(D14:G14,(D$1:G$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Mobile Development</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Cross-platform app implementation and testing</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="H15" s="24">
-        <f>SUM(D15:G15)</f>
-        <v/>
-      </c>
-      <c r="I15" s="24">
-        <f>SUMPRODUCT(D15:G15,(D$1:G$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Mobile Development</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Cross-platform app implementation and testing</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="G16" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="H16" s="24">
-        <f>SUM(D16:G16)</f>
-        <v/>
-      </c>
-      <c r="I16" s="24">
-        <f>SUMPRODUCT(D16:G16,(D$1:G$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Launch</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>App store submission, UAT and go-live</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="E17" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="H17" s="24">
-        <f>SUM(D17:G17)</f>
-        <v/>
-      </c>
-      <c r="I17" s="24">
-        <f>SUMPRODUCT(D17:G17,(D$1:G$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Launch</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>App store submission, UAT and go-live</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="F18" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="H18" s="24">
-        <f>SUM(D18:G18)</f>
-        <v/>
-      </c>
-      <c r="I18" s="24">
-        <f>SUMPRODUCT(D18:G18,(D$1:G$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>Launch</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>App store submission, UAT and go-live</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="G19" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="H19" s="24">
-        <f>SUM(D19:G19)</f>
-        <v/>
-      </c>
-      <c r="I19" s="24">
-        <f>SUMPRODUCT(D19:G19,(D$1:G$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Subtotal — Engineering</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="D20" s="25">
-        <f>SUM(D7,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17,D18,D19)</f>
-        <v/>
-      </c>
-      <c r="E20" s="25">
-        <f>SUM(E7,E8,E9,E10,E11,E12,E13,E14,E15,E16,E17,E18,E19)</f>
-        <v/>
-      </c>
-      <c r="F20" s="25">
-        <f>SUM(F7,F8,F9,F10,F11,F12,F13,F14,F15,F16,F17,F18,F19)</f>
-        <v/>
-      </c>
-      <c r="G20" s="25">
-        <f>SUM(G7,G8,G9,G10,G11,G12,G13,G14,G15,G16,G17,G18,G19)</f>
-        <v/>
-      </c>
-      <c r="H20" s="26">
-        <f>SUM(D20:G20)</f>
-        <v/>
-      </c>
-      <c r="I20" s="26">
-        <f>SUMPRODUCT(D20:G20,(D$1:G$1="Y")*1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr"/>
-      <c r="C21" s="11" t="inlineStr"/>
-      <c r="H21" s="27">
-        <f>SUM(H6,H20)</f>
-        <v/>
-      </c>
-      <c r="I21" s="27">
-        <f>SUM(I6,I20)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4827,59 +3924,59 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B3" s="28" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>Offline sync complexity underestimated</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="C3" s="21" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
       </c>
-      <c r="D3" s="28" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t>3, 4</t>
         </is>
       </c>
-      <c r="E3" s="28" t="n">
+      <c r="E3" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="F3" s="28" t="n">
+      <c r="F3" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="21">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="H3" s="28">
+      <c r="H3" s="21">
         <f>IF(G3&gt;=15,"CRITICAL",IF(G3&gt;=10,"HIGH",IF(G3&gt;=5,"MEDIUM","LOW")))</f>
         <v/>
       </c>
-      <c r="I3" s="28" t="inlineStr">
+      <c r="I3" s="21" t="inlineStr">
         <is>
           <t>Mitigate</t>
         </is>
       </c>
-      <c r="J3" s="28" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t>Proof-of-concept spike in Discovery; adopt proven sync library</t>
         </is>
       </c>
-      <c r="K3" s="28" t="inlineStr">
+      <c r="K3" s="21" t="inlineStr">
         <is>
           <t>BED</t>
         </is>
       </c>
-      <c r="L3" s="28" t="n">
+      <c r="L3" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="M3" s="28">
+      <c r="M3" s="21">
         <f>L3*550</f>
         <v/>
       </c>
@@ -5001,59 +4098,59 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="B6" s="28" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>Scope creep from stakeholder change requests</t>
         </is>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>Organizational</t>
         </is>
       </c>
-      <c r="D6" s="28" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>1, 2, 5</t>
         </is>
       </c>
-      <c r="E6" s="28" t="n">
+      <c r="E6" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="28" t="n">
+      <c r="F6" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="21">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="21">
         <f>IF(G6&gt;=15,"CRITICAL",IF(G6&gt;=10,"HIGH",IF(G6&gt;=5,"MEDIUM","LOW")))</f>
         <v/>
       </c>
-      <c r="I6" s="28" t="inlineStr">
+      <c r="I6" s="21" t="inlineStr">
         <is>
           <t>Mitigate</t>
         </is>
       </c>
-      <c r="J6" s="28" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t>Formal change control process; freeze scope after Phase 2</t>
         </is>
       </c>
-      <c r="K6" s="28" t="inlineStr">
+      <c r="K6" s="21" t="inlineStr">
         <is>
           <t>PO</t>
         </is>
       </c>
-      <c r="L6" s="28" t="n">
+      <c r="L6" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="M6" s="28">
+      <c r="M6" s="21">
         <f>L6*550</f>
         <v/>
       </c>
@@ -5138,11 +4235,11 @@
         </is>
       </c>
       <c r="L10">
-        <f>L9*0.1</f>
+        <f>(WBS!H39*(1+0.1+0.05)+L9)*0.1</f>
         <v/>
       </c>
       <c r="M10">
-        <f>M9*0.1</f>
+        <f>(WBS!H39*(1+0.1+0.05)+L9)*0.1*550</f>
         <v/>
       </c>
     </row>
@@ -5151,17 +4248,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -5512,7 +4609,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Total PERT Effort (pd)</t>
+          <t>Tech PERT Effort (PD)</t>
         </is>
       </c>
       <c r="B9">
@@ -5523,140 +4620,176 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Total Billable Effort (pd)</t>
+          <t>PM Overhead (+10%) (PD)</t>
         </is>
       </c>
       <c r="B10">
-        <f>WBS!S39</f>
+        <f>B9*0.1</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Billable Ratio</t>
+          <t>DevOps Overhead (+5%) (PD)</t>
         </is>
       </c>
       <c r="B11">
-        <f>B10/B9</f>
+        <f>B9*0.05</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>σ Total Duration</t>
+          <t>Subtotal Tech + Overhead (PD)</t>
         </is>
       </c>
       <c r="B12">
-        <f>SQRT(SUMPRODUCT(K2:K6,K2:K6))</f>
+        <f>B9+B10+B11</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CI 68% Lower</t>
+          <t>Contingency per-risk (PD)</t>
         </is>
       </c>
       <c r="B13">
-        <f>J7-B12</f>
+        <f>Risks!L9</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CI 68% Upper</t>
+          <t>Low Band</t>
         </is>
       </c>
       <c r="B14">
-        <f>J7+B12</f>
+        <f>B12+B13</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CI 95% Lower</t>
+          <t>Management Reserve (10%) (PD)</t>
         </is>
       </c>
       <c r="B15">
-        <f>J7-2*B12</f>
+        <f>B14*0.1</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CI 95% Upper</t>
+          <t>Medium Band (recommended)</t>
         </is>
       </c>
       <c r="B16">
-        <f>J7+2*B12</f>
+        <f>B14+B15</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Total Contingency</t>
+          <t>High Band</t>
         </is>
       </c>
       <c r="B17">
-        <f>Risks!L9</f>
+        <f>B16*(1+0.12)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Management Reserve</t>
+          <t>Total Billable Effort (PD)</t>
         </is>
       </c>
       <c r="B18">
-        <f>Risks!L10</f>
+        <f>WBS!S39</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Adjusted PERT Effort (pd)</t>
+          <t>Billable Ratio</t>
         </is>
       </c>
       <c r="B19">
-        <f>B9+B17+B18</f>
+        <f>B18/B9</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>Effort by Team</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Calendar Duration (weeks)</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>Effort by Team (PD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n">
+        <v>84.00000000000001</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="B22">
-        <f>Resources!H6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="B23">
-        <f>Resources!H20</f>
-        <v/>
+      <c r="B25" s="16" t="n">
+        <v>15.83333333333333</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>Sensitivity Scenarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Optimistic: ~85% of Fascia MEDIA — best-case execution for 3-mobile-app</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Realistic: Fascia MEDIA — current best estimate including overhead and MR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Pessimistic: ~115% of Fascia MEDIA — material slippage on critical path</t>
+        </is>
       </c>
     </row>
   </sheetData>
